--- a/data/stx_xlsx/LAMMb.ST.xlsx
+++ b/data/stx_xlsx/LAMMb.ST.xlsx
@@ -13189,11 +13189,21 @@
       <c r="A92" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
+      <c r="B92" s="15">
+        <v>122.58</v>
+      </c>
+      <c r="C92" s="15">
+        <v>136.02</v>
+      </c>
+      <c r="D92" s="15">
+        <v>117.19</v>
+      </c>
+      <c r="E92" s="18">
+        <v>78.31</v>
+      </c>
+      <c r="F92" s="18">
+        <v>45.01</v>
+      </c>
       <c r="G92" s="18">
         <v>15.25</v>
       </c>
@@ -13203,21 +13213,47 @@
       <c r="I92" s="18">
         <v>15.91</v>
       </c>
-      <c r="J92" s="19"/>
-      <c r="K92" s="19"/>
-      <c r="L92" s="19"/>
-      <c r="M92" s="19"/>
-      <c r="N92" s="19"/>
+      <c r="J92" s="15">
+        <v>128.98</v>
+      </c>
+      <c r="K92" s="15">
+        <v>115.79</v>
+      </c>
+      <c r="L92" s="18">
+        <v>53.48</v>
+      </c>
+      <c r="M92" s="18">
+        <v>47.06</v>
+      </c>
+      <c r="N92" s="18">
+        <v>71.91</v>
+      </c>
       <c r="O92" s="19"/>
       <c r="P92" s="19"/>
-      <c r="Q92" s="19"/>
-      <c r="R92" s="19"/>
-      <c r="S92" s="19"/>
-      <c r="T92" s="19"/>
-      <c r="U92" s="19"/>
-      <c r="V92" s="19"/>
-      <c r="W92" s="19"/>
-      <c r="X92" s="19"/>
+      <c r="Q92" s="18">
+        <v>17.44</v>
+      </c>
+      <c r="R92" s="18">
+        <v>25.65</v>
+      </c>
+      <c r="S92" s="18">
+        <v>33.79</v>
+      </c>
+      <c r="T92" s="18">
+        <v>17.75</v>
+      </c>
+      <c r="U92" s="18">
+        <v>19.94</v>
+      </c>
+      <c r="V92" s="18">
+        <v>20.97</v>
+      </c>
+      <c r="W92" s="18">
+        <v>21.56</v>
+      </c>
+      <c r="X92" s="18">
+        <v>21.56</v>
+      </c>
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
